--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,6 +1028,228 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125555807</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91186</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sågknösen, Sågknösen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>632479</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6555519</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125554570</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91186</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågknösen, Sågknösen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>632449</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6555558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1033,12 +1033,7 @@
         <v>125555807</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,12 +1139,7 @@
         <v>125554570</v>
       </c>
       <c r="B6" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>125555807</v>
       </c>
       <c r="B5" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>125554570</v>
       </c>
       <c r="B6" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>125555807</v>
       </c>
       <c r="B5" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>125554570</v>
       </c>
       <c r="B6" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125555807</v>
+        <v>125554570</v>
       </c>
       <c r="B5" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632479</v>
+        <v>632449</v>
       </c>
       <c r="R5" t="n">
-        <v>6555519</v>
+        <v>6555558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125554570</v>
+        <v>125555807</v>
       </c>
       <c r="B6" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632449</v>
+        <v>632479</v>
       </c>
       <c r="R6" t="n">
-        <v>6555558</v>
+        <v>6555519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125554570</v>
+        <v>125555807</v>
       </c>
       <c r="B5" t="n">
         <v>91252</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632449</v>
+        <v>632479</v>
       </c>
       <c r="R5" t="n">
-        <v>6555558</v>
+        <v>6555519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125555807</v>
+        <v>125554570</v>
       </c>
       <c r="B6" t="n">
         <v>91252</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632479</v>
+        <v>632449</v>
       </c>
       <c r="R6" t="n">
-        <v>6555519</v>
+        <v>6555558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>125555807</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>125554570</v>
       </c>
       <c r="B6" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>125555807</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>125554570</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125555807</v>
+        <v>125554570</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632479</v>
+        <v>632449</v>
       </c>
       <c r="R5" t="n">
-        <v>6555519</v>
+        <v>6555558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125554570</v>
+        <v>125555807</v>
       </c>
       <c r="B6" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632449</v>
+        <v>632479</v>
       </c>
       <c r="R6" t="n">
-        <v>6555558</v>
+        <v>6555519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,116 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131900477</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93121</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ö Långsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>632475</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6555521</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>131900477</v>
       </c>
       <c r="B7" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>131900477</v>
       </c>
       <c r="B7" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>131900477</v>
       </c>
       <c r="B7" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>131900477</v>
       </c>
       <c r="B7" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>131900477</v>
       </c>
       <c r="B7" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>131900477</v>
       </c>
       <c r="B7" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1152075</v>
       </c>
       <c r="B2" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632486.2937839275</v>
+        <v>632486</v>
       </c>
       <c r="R2" t="n">
-        <v>6555583.839647494</v>
+        <v>6555584</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2004-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1651492</v>
+        <v>131900477</v>
       </c>
       <c r="B3" t="n">
-        <v>89411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +788,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsjön (51m):s Ö sida, Srm</t>
+          <t>Ö Långsjön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632486.2937839275</v>
+        <v>632475</v>
       </c>
       <c r="R3" t="n">
-        <v>6555583.839647494</v>
+        <v>6555521</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,38 +868,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7036765</v>
+        <v>1651492</v>
       </c>
       <c r="B4" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,38 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsjön vid Klämmingen, Srm</t>
+          <t>Långsjön (51m):s Ö sida, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632565.4073123706</v>
+        <v>632486</v>
       </c>
       <c r="R4" t="n">
-        <v>6555529.034958799</v>
+        <v>6555584</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -983,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-02-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-02-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-11-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +992,7 @@
         <v>125554570</v>
       </c>
       <c r="B5" t="n">
-        <v>91258</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1098,7 @@
         <v>125555807</v>
       </c>
       <c r="B6" t="n">
-        <v>91258</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,55 +1201,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131900477</v>
+        <v>128514405</v>
       </c>
       <c r="B7" t="n">
-        <v>93186</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ö Långsjön, Srm</t>
+          <t>Väsby-Långsjö, Väsby-Långsjö, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632475</v>
+        <v>632785</v>
       </c>
       <c r="R7" t="n">
-        <v>6555521</v>
+        <v>6555513</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,17 +1266,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,7 +1290,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,6 +1305,221 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131900473</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ö Långsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>632418</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6555819</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7036765</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långsjön vid Klämmingen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>632565</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6555529</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2009-02-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2009-02-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20124-2022 artfynd.xlsx
+++ b/artfynd/A 20124-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1152075</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1651492</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125554570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125555807</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514405</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900473</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,8 +1560,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7036765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>